--- a/Team-Data/2007-08/12-4-2007-08.xlsx
+++ b/Team-Data/2007-08/12-4-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,25 +728,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
         <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.412</v>
+        <v>0.438</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>34.4</v>
+        <v>34.6</v>
       </c>
       <c r="J2" t="n">
-        <v>77.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="K2" t="n">
         <v>0.444</v>
@@ -688,31 +755,31 @@
         <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.311</v>
+        <v>0.309</v>
       </c>
       <c r="O2" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.769</v>
+        <v>0.76</v>
       </c>
       <c r="R2" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="S2" t="n">
-        <v>28.5</v>
+        <v>28.8</v>
       </c>
       <c r="T2" t="n">
-        <v>40.5</v>
+        <v>40.9</v>
       </c>
       <c r="U2" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V2" t="n">
         <v>15.9</v>
@@ -721,37 +788,37 @@
         <v>7.6</v>
       </c>
       <c r="X2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y2" t="n">
         <v>5.8</v>
       </c>
-      <c r="Y2" t="n">
-        <v>6</v>
-      </c>
       <c r="Z2" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>93.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2</v>
+        <v>-1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG2" t="n">
         <v>19</v>
       </c>
       <c r="AH2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>24</v>
@@ -760,7 +827,7 @@
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL2" t="n">
         <v>28</v>
@@ -769,16 +836,16 @@
         <v>27</v>
       </c>
       <c r="AN2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
         <v>12</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
         <v>10</v>
@@ -787,28 +854,28 @@
         <v>28</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU2" t="n">
         <v>24</v>
       </c>
       <c r="AV2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
         <v>2</v>
       </c>
       <c r="AY2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB2" t="n">
         <v>23</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>13.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -936,16 +1003,16 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM3" t="n">
         <v>13</v>
@@ -957,7 +1024,7 @@
         <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
         <v>14</v>
@@ -969,7 +1036,7 @@
         <v>2</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
@@ -978,7 +1045,7 @@
         <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX3" t="n">
         <v>24</v>
@@ -987,13 +1054,13 @@
         <v>20</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-5.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF4" t="n">
         <v>21</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>17</v>
       </c>
       <c r="AG4" t="n">
         <v>21</v>
@@ -1121,10 +1188,10 @@
         <v>26</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
         <v>13</v>
@@ -1136,10 +1203,10 @@
         <v>6</v>
       </c>
       <c r="AO4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
         <v>29</v>
@@ -1148,7 +1215,7 @@
         <v>3</v>
       </c>
       <c r="AS4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT4" t="n">
         <v>20</v>
@@ -1157,7 +1224,7 @@
         <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AW4" t="n">
         <v>9</v>
@@ -1178,7 +1245,7 @@
         <v>25</v>
       </c>
       <c r="BC4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE5" t="n">
         <v>27</v>
@@ -1312,16 +1379,16 @@
         <v>22</v>
       </c>
       <c r="AM5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO5" t="n">
         <v>26</v>
       </c>
       <c r="AP5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ5" t="n">
         <v>18</v>
@@ -1330,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
         <v>5</v>
@@ -1339,7 +1406,7 @@
         <v>19</v>
       </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW5" t="n">
         <v>7</v>
@@ -1351,16 +1418,16 @@
         <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB5" t="n">
         <v>30</v>
       </c>
       <c r="BC5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -1389,67 +1456,67 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
         <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>0.474</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>35.8</v>
+        <v>36.3</v>
       </c>
       <c r="J6" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0.434</v>
+        <v>0.439</v>
       </c>
       <c r="L6" t="n">
         <v>7.2</v>
       </c>
       <c r="M6" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.364</v>
+        <v>0.363</v>
       </c>
       <c r="O6" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
-        <v>25.3</v>
+        <v>25.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.702</v>
+        <v>0.698</v>
       </c>
       <c r="R6" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="S6" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="T6" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="U6" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="V6" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W6" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y6" t="n">
         <v>5.2</v>
@@ -1458,40 +1525,40 @@
         <v>22.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="AB6" t="n">
-        <v>96.59999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>-4.5</v>
+        <v>-3.6</v>
       </c>
       <c r="AD6" t="n">
         <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AJ6" t="n">
         <v>8</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM6" t="n">
         <v>10</v>
@@ -1503,25 +1570,25 @@
         <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>26</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
         <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
         <v>26</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
         <v>18</v>
@@ -1536,13 +1603,13 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>6</v>
       </c>
       <c r="AF7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG7" t="n">
         <v>7</v>
@@ -1673,7 +1740,7 @@
         <v>10</v>
       </c>
       <c r="AL7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM7" t="n">
         <v>17</v>
@@ -1682,7 +1749,7 @@
         <v>23</v>
       </c>
       <c r="AO7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP7" t="n">
         <v>9</v>
@@ -1697,13 +1764,13 @@
         <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
         <v>15</v>
       </c>
       <c r="AV7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW7" t="n">
         <v>30</v>
@@ -1721,7 +1788,7 @@
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
         <v>9</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -1831,10 +1898,10 @@
         <v>5.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF8" t="n">
         <v>9</v>
@@ -1855,7 +1922,7 @@
         <v>11</v>
       </c>
       <c r="AL8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM8" t="n">
         <v>7</v>
@@ -1867,13 +1934,13 @@
         <v>5</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="n">
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>6</v>
@@ -1885,7 +1952,7 @@
         <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -1935,94 +2002,94 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.706</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>38.5</v>
+        <v>38.3</v>
       </c>
       <c r="J9" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.479</v>
+        <v>0.476</v>
       </c>
       <c r="L9" t="n">
         <v>5.6</v>
       </c>
       <c r="M9" t="n">
-        <v>15.4</v>
+        <v>15.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.366</v>
+        <v>0.357</v>
       </c>
       <c r="O9" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="P9" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.735</v>
+        <v>0.726</v>
       </c>
       <c r="R9" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S9" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="T9" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U9" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="V9" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="W9" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X9" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>101</v>
+        <v>100.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF9" t="n">
         <v>5</v>
       </c>
       <c r="AG9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH9" t="n">
         <v>19</v>
@@ -2034,25 +2101,25 @@
         <v>17</v>
       </c>
       <c r="AK9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM9" t="n">
         <v>21</v>
       </c>
-      <c r="AM9" t="n">
-        <v>23</v>
-      </c>
       <c r="AN9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AO9" t="n">
         <v>17</v>
       </c>
       <c r="AP9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR9" t="n">
         <v>13</v>
@@ -2067,28 +2134,28 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
         <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY9" t="n">
         <v>1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>1.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF10" t="n">
         <v>10</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
         <v>2</v>
@@ -2225,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
         <v>16</v>
@@ -2237,16 +2304,16 @@
         <v>28</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
         <v>17</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV10" t="n">
         <v>6</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>1.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF11" t="n">
         <v>14</v>
@@ -2404,10 +2471,10 @@
         <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
         <v>24</v>
@@ -2416,7 +2483,7 @@
         <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR11" t="n">
         <v>6</v>
@@ -2425,16 +2492,16 @@
         <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
         <v>15</v>
       </c>
       <c r="AV11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX11" t="n">
         <v>18</v>
@@ -2443,10 +2510,10 @@
         <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB11" t="n">
         <v>19</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -2481,106 +2548,106 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
         <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.474</v>
+        <v>0.5</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.9</v>
+        <v>37.4</v>
       </c>
       <c r="J12" t="n">
-        <v>87.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.434</v>
+        <v>0.432</v>
       </c>
       <c r="L12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="M12" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.333</v>
+        <v>0.337</v>
       </c>
       <c r="O12" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="P12" t="n">
-        <v>26.3</v>
+        <v>26.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.748</v>
+        <v>0.744</v>
       </c>
       <c r="R12" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S12" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T12" t="n">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="U12" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V12" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="W12" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="X12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Y12" t="n">
         <v>5.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>103</v>
+        <v>102.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="AD12" t="n">
         <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH12" t="n">
         <v>16</v>
       </c>
-      <c r="AH12" t="n">
-        <v>18</v>
-      </c>
       <c r="AI12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
         <v>8</v>
@@ -2589,16 +2656,16 @@
         <v>4</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
         <v>13</v>
       </c>
       <c r="AP12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR12" t="n">
         <v>5</v>
@@ -2616,10 +2683,10 @@
         <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AX12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY12" t="n">
         <v>25</v>
@@ -2631,7 +2698,7 @@
         <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC12" t="n">
         <v>16</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -2663,67 +2730,67 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="H13" t="n">
         <v>48</v>
       </c>
       <c r="I13" t="n">
-        <v>33.1</v>
+        <v>33.4</v>
       </c>
       <c r="J13" t="n">
-        <v>79.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.419</v>
+        <v>0.421</v>
       </c>
       <c r="L13" t="n">
         <v>5.9</v>
       </c>
       <c r="M13" t="n">
-        <v>16.3</v>
+        <v>15.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.364</v>
+        <v>0.372</v>
       </c>
       <c r="O13" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="P13" t="n">
-        <v>27.8</v>
+        <v>28.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R13" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="S13" t="n">
-        <v>32.6</v>
+        <v>33.2</v>
       </c>
       <c r="T13" t="n">
-        <v>42.4</v>
+        <v>43.4</v>
       </c>
       <c r="U13" t="n">
         <v>20.1</v>
       </c>
       <c r="V13" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="W13" t="n">
         <v>6.1</v>
       </c>
       <c r="X13" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="Y13" t="n">
         <v>5.3</v>
@@ -2732,25 +2799,25 @@
         <v>21.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.2</v>
+        <v>95.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>-5.6</v>
+        <v>-5.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AE13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH13" t="n">
         <v>19</v>
@@ -2759,58 +2826,58 @@
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
         <v>20</v>
       </c>
       <c r="AN13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AO13" t="n">
         <v>6</v>
       </c>
       <c r="AP13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
         <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AU13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV13" t="n">
         <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
         <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -2845,64 +2912,64 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.556</v>
+        <v>0.529</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>38.1</v>
+        <v>37.7</v>
       </c>
       <c r="J14" t="n">
         <v>81.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.469</v>
+        <v>0.464</v>
       </c>
       <c r="L14" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.357</v>
+        <v>0.35</v>
       </c>
       <c r="O14" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="P14" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.779</v>
+        <v>0.783</v>
       </c>
       <c r="R14" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="S14" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="T14" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="V14" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="W14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>4.6</v>
@@ -2911,28 +2978,28 @@
         <v>5.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.1</v>
+        <v>105.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF14" t="n">
         <v>10</v>
       </c>
       <c r="AG14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH14" t="n">
         <v>19</v>
@@ -2941,28 +3008,28 @@
         <v>7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP14" t="n">
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR14" t="n">
         <v>16</v>
@@ -2974,10 +3041,10 @@
         <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW14" t="n">
         <v>5</v>
@@ -2989,7 +3056,7 @@
         <v>17</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
         <v>7</v>
@@ -2998,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -3105,10 +3172,10 @@
         <v>-1</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF15" t="n">
         <v>23</v>
@@ -3120,7 +3187,7 @@
         <v>15</v>
       </c>
       <c r="AI15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ15" t="n">
         <v>16</v>
@@ -3144,7 +3211,7 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
         <v>24</v>
@@ -3153,7 +3220,7 @@
         <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU15" t="n">
         <v>13</v>
@@ -3165,7 +3232,7 @@
         <v>29</v>
       </c>
       <c r="AX15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY15" t="n">
         <v>16</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>27</v>
@@ -3317,7 +3384,7 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>23</v>
@@ -3332,7 +3399,7 @@
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
@@ -3341,13 +3408,13 @@
         <v>27</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
         <v>8</v>
       </c>
       <c r="AX16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY16" t="n">
         <v>2</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -3391,37 +3458,37 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
         <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="J17" t="n">
-        <v>78.8</v>
+        <v>79</v>
       </c>
       <c r="K17" t="n">
-        <v>0.464</v>
+        <v>0.466</v>
       </c>
       <c r="L17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M17" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.323</v>
+        <v>0.324</v>
       </c>
       <c r="O17" t="n">
         <v>17.1</v>
@@ -3430,55 +3497,55 @@
         <v>23.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.733</v>
+        <v>0.729</v>
       </c>
       <c r="R17" t="n">
         <v>11.5</v>
       </c>
       <c r="S17" t="n">
-        <v>29.6</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="U17" t="n">
         <v>21</v>
       </c>
       <c r="V17" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W17" t="n">
         <v>6.1</v>
       </c>
       <c r="X17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="AA17" t="n">
         <v>21.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.90000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.5</v>
+        <v>-4.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF17" t="n">
         <v>10</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
         <v>19</v>
@@ -3490,10 +3557,10 @@
         <v>24</v>
       </c>
       <c r="AK17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AL17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM17" t="n">
         <v>26</v>
@@ -3502,7 +3569,7 @@
         <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
@@ -3514,16 +3581,16 @@
         <v>15</v>
       </c>
       <c r="AS17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT17" t="n">
         <v>24</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>22</v>
       </c>
       <c r="AU17" t="n">
         <v>14</v>
       </c>
       <c r="AV17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW17" t="n">
         <v>26</v>
@@ -3532,10 +3599,10 @@
         <v>6</v>
       </c>
       <c r="AY17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
         <v>14</v>
@@ -3544,7 +3611,7 @@
         <v>20</v>
       </c>
       <c r="BC17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>0.125</v>
+        <v>0.133</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
@@ -3597,67 +3664,67 @@
         <v>0.445</v>
       </c>
       <c r="L18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.352</v>
+        <v>0.363</v>
       </c>
       <c r="O18" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="P18" t="n">
-        <v>20.3</v>
+        <v>19.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.713</v>
+        <v>0.717</v>
       </c>
       <c r="R18" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S18" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T18" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="U18" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="V18" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="W18" t="n">
         <v>7.7</v>
       </c>
       <c r="X18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y18" t="n">
         <v>4.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="AC18" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
       </c>
       <c r="AF18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG18" t="n">
         <v>30</v>
@@ -3678,10 +3745,10 @@
         <v>16</v>
       </c>
       <c r="AM18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3693,19 +3760,19 @@
         <v>24</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
         <v>29</v>
       </c>
       <c r="AT18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="n">
         <v>28</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -3755,64 +3822,64 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="n">
         <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="H19" t="n">
         <v>48.6</v>
       </c>
       <c r="I19" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="J19" t="n">
-        <v>74.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.423</v>
+        <v>0.418</v>
       </c>
       <c r="L19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M19" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.318</v>
+        <v>0.307</v>
       </c>
       <c r="O19" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="P19" t="n">
-        <v>29.3</v>
+        <v>29</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.744</v>
+        <v>0.748</v>
       </c>
       <c r="R19" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S19" t="n">
-        <v>30.3</v>
+        <v>29.9</v>
       </c>
       <c r="T19" t="n">
-        <v>40.4</v>
+        <v>39.9</v>
       </c>
       <c r="U19" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="V19" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="W19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="X19" t="n">
         <v>4.9</v>
@@ -3821,31 +3888,31 @@
         <v>4.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.9</v>
+        <v>24.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>90.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.7</v>
+        <v>-7.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AF19" t="n">
         <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3854,40 +3921,40 @@
         <v>30</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AM19" t="n">
         <v>14</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AO19" t="n">
         <v>7</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AU19" t="n">
         <v>9</v>
       </c>
       <c r="AV19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AW19" t="n">
         <v>24</v>
@@ -3899,7 +3966,7 @@
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA19" t="n">
         <v>3</v>
@@ -3908,7 +3975,7 @@
         <v>28</v>
       </c>
       <c r="BC19" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -4015,19 +4082,19 @@
         <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
         <v>6</v>
       </c>
       <c r="AF20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG20" t="n">
         <v>7</v>
       </c>
       <c r="AH20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI20" t="n">
         <v>18</v>
@@ -4036,7 +4103,7 @@
         <v>11</v>
       </c>
       <c r="AK20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
@@ -4072,7 +4139,7 @@
         <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX20" t="n">
         <v>28</v>
@@ -4084,13 +4151,13 @@
         <v>4</v>
       </c>
       <c r="BA20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -4215,7 +4282,7 @@
         <v>23</v>
       </c>
       <c r="AJ21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK21" t="n">
         <v>27</v>
@@ -4224,7 +4291,7 @@
         <v>25</v>
       </c>
       <c r="AM21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN21" t="n">
         <v>25</v>
@@ -4242,10 +4309,10 @@
         <v>4</v>
       </c>
       <c r="AS21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4482,7 @@
         <v>10</v>
       </c>
       <c r="AP22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ22" t="n">
         <v>23</v>
@@ -4427,13 +4494,13 @@
         <v>1</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
         <v>12</v>
       </c>
       <c r="AV22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW22" t="n">
         <v>25</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
         <v>25</v>
@@ -4573,22 +4640,22 @@
         <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI23" t="n">
         <v>25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL23" t="n">
         <v>29</v>
       </c>
       <c r="AM23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN23" t="n">
         <v>30</v>
@@ -4597,7 +4664,7 @@
         <v>18</v>
       </c>
       <c r="AP23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ23" t="n">
         <v>25</v>
@@ -4621,22 +4688,22 @@
         <v>19</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY23" t="n">
         <v>14</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB23" t="n">
         <v>27</v>
       </c>
       <c r="BC23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -4665,64 +4732,64 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>0.778</v>
+        <v>0.765</v>
       </c>
       <c r="H24" t="n">
         <v>48</v>
       </c>
       <c r="I24" t="n">
-        <v>41.7</v>
+        <v>41.5</v>
       </c>
       <c r="J24" t="n">
-        <v>85.40000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K24" t="n">
         <v>0.488</v>
       </c>
       <c r="L24" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="M24" t="n">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.366</v>
+        <v>0.373</v>
       </c>
       <c r="O24" t="n">
-        <v>17.4</v>
+        <v>16.8</v>
       </c>
       <c r="P24" t="n">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.783</v>
+        <v>0.773</v>
       </c>
       <c r="R24" t="n">
         <v>8.5</v>
       </c>
       <c r="S24" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="T24" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="U24" t="n">
-        <v>26.5</v>
+        <v>25.8</v>
       </c>
       <c r="V24" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W24" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X24" t="n">
         <v>5.7</v>
@@ -4734,19 +4801,19 @@
         <v>19.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.1</v>
+        <v>108.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF24" t="n">
         <v>3</v>
@@ -4767,22 +4834,22 @@
         <v>2</v>
       </c>
       <c r="AL24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AM24" t="n">
         <v>3</v>
       </c>
       <c r="AN24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
@@ -4791,13 +4858,13 @@
         <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU24" t="n">
         <v>2</v>
       </c>
       <c r="AV24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW24" t="n">
         <v>6</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>-5.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF25" t="n">
         <v>26</v>
@@ -4952,10 +5019,10 @@
         <v>18</v>
       </c>
       <c r="AM25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
         <v>28</v>
@@ -4970,7 +5037,7 @@
         <v>25</v>
       </c>
       <c r="AS25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT25" t="n">
         <v>29</v>
@@ -4979,7 +5046,7 @@
         <v>17</v>
       </c>
       <c r="AV25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW25" t="n">
         <v>28</v>
@@ -5000,7 +5067,7 @@
         <v>26</v>
       </c>
       <c r="BC25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -5029,49 +5096,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
         <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>0.412</v>
+        <v>0.375</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>35.5</v>
+        <v>35.3</v>
       </c>
       <c r="J26" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.451</v>
+        <v>0.448</v>
       </c>
       <c r="L26" t="n">
         <v>5.2</v>
       </c>
       <c r="M26" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.344</v>
+        <v>0.336</v>
       </c>
       <c r="O26" t="n">
-        <v>24.8</v>
+        <v>24.1</v>
       </c>
       <c r="P26" t="n">
-        <v>30.8</v>
+        <v>29.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.805</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S26" t="n">
         <v>29.6</v>
@@ -5083,10 +5150,10 @@
         <v>16.1</v>
       </c>
       <c r="V26" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="W26" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X26" t="n">
         <v>3.6</v>
@@ -5095,31 +5162,31 @@
         <v>5.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>100.9</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>-3</v>
+        <v>-3.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AG26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI26" t="n">
         <v>21</v>
@@ -5128,7 +5195,7 @@
         <v>25</v>
       </c>
       <c r="AK26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>23</v>
@@ -5137,22 +5204,22 @@
         <v>24</v>
       </c>
       <c r="AN26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO26" t="n">
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT26" t="n">
         <v>28</v>
@@ -5161,7 +5228,7 @@
         <v>30</v>
       </c>
       <c r="AV26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW26" t="n">
         <v>17</v>
@@ -5170,19 +5237,19 @@
         <v>29</v>
       </c>
       <c r="AY26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA26" t="n">
         <v>1</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>9.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -5313,7 +5380,7 @@
         <v>3</v>
       </c>
       <c r="AL27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM27" t="n">
         <v>6</v>
@@ -5328,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR27" t="n">
         <v>26</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>29</v>
@@ -5483,34 +5550,34 @@
         <v>29</v>
       </c>
       <c r="AH28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM28" t="n">
         <v>29</v>
       </c>
       <c r="AN28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
         <v>14</v>
@@ -5528,7 +5595,7 @@
         <v>30</v>
       </c>
       <c r="AW28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX28" t="n">
         <v>13</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>4.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>10</v>
@@ -5674,10 +5741,10 @@
         <v>7</v>
       </c>
       <c r="AK29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM29" t="n">
         <v>9</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -5757,94 +5824,94 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
         <v>13</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.722</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="J30" t="n">
-        <v>81.3</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.494</v>
+        <v>0.495</v>
       </c>
       <c r="L30" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O30" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="P30" t="n">
-        <v>29.7</v>
+        <v>30.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R30" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S30" t="n">
         <v>29.8</v>
       </c>
       <c r="T30" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U30" t="n">
-        <v>26.9</v>
+        <v>27.2</v>
       </c>
       <c r="V30" t="n">
         <v>16.2</v>
       </c>
       <c r="W30" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y30" t="n">
         <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="AB30" t="n">
         <v>107.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD30" t="n">
         <v>2</v>
       </c>
       <c r="AE30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF30" t="n">
         <v>5</v>
       </c>
-      <c r="AF30" t="n">
-        <v>6</v>
-      </c>
       <c r="AG30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH30" t="n">
         <v>19</v>
@@ -5853,7 +5920,7 @@
         <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AK30" t="n">
         <v>1</v>
@@ -5865,22 +5932,22 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO30" t="n">
         <v>4</v>
       </c>
       <c r="AP30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ30" t="n">
         <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
         <v>19</v>
@@ -5889,19 +5956,19 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
         <v>23</v>
       </c>
       <c r="AY30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AZ30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA30" t="n">
         <v>4</v>
@@ -5910,7 +5977,7 @@
         <v>3</v>
       </c>
       <c r="BC30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
@@ -6017,19 +6084,19 @@
         <v>-0.4</v>
       </c>
       <c r="AD31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE31" t="n">
         <v>16</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>17</v>
       </c>
       <c r="AF31" t="n">
         <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI31" t="n">
         <v>13</v>
@@ -6056,7 +6123,7 @@
         <v>10</v>
       </c>
       <c r="AQ31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR31" t="n">
         <v>9</v>
@@ -6077,7 +6144,7 @@
         <v>16</v>
       </c>
       <c r="AX31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY31" t="n">
         <v>8</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-4-2007-08</t>
+          <t>2007-12-04</t>
         </is>
       </c>
     </row>
